--- a/gte/nodes/HPT/turbine_parameters.xlsx
+++ b/gte/nodes/HPT/turbine_parameters.xlsx
@@ -1123,106 +1123,106 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.886829876038094</v>
+        <v>0.88661849100439383</v>
       </c>
       <c r="C3">
         <v>1773</v>
       </c>
       <c r="D3">
-        <v>1758.9562299548395</v>
+        <v>1758.9932072717177</v>
       </c>
       <c r="E3">
-        <v>1394.1636317648961</v>
+        <v>1394.1838085136349</v>
       </c>
       <c r="F3">
         <v>1878.5536664504473</v>
       </c>
       <c r="G3">
-        <v>1493.4468943669831</v>
+        <v>1493.0928812604607</v>
       </c>
       <c r="H3">
-        <v>1490.9601461647246</v>
+        <v>1491.374610104014</v>
       </c>
       <c r="I3">
         <v>1768.9494547516442</v>
       </c>
       <c r="J3">
-        <v>1411.2420973554488</v>
+        <v>1410.5065331557605</v>
       </c>
       <c r="K3">
-        <v>1385.2936703957228</v>
+        <v>1385.1464831526919</v>
       </c>
       <c r="L3">
         <v>2731.8</v>
       </c>
       <c r="M3">
-        <v>2414.4666913734436</v>
+        <v>2413.7074417616545</v>
       </c>
       <c r="N3">
-        <v>872.8720844382259</v>
+        <v>870.4517592730466</v>
       </c>
       <c r="O3">
         <v>2705.1966216148621</v>
       </c>
       <c r="P3">
-        <v>941.6483665161013</v>
+        <v>939.17006936673044</v>
       </c>
       <c r="Q3">
-        <v>850.00194622173285</v>
+        <v>847.21940418293445</v>
       </c>
       <c r="R3">
         <v>5.34064271677014</v>
       </c>
       <c r="S3">
-        <v>4.7580047901266287</v>
+        <v>4.7564086043237728</v>
       </c>
       <c r="T3">
-        <v>2.1701879135223678</v>
+        <v>2.1641390095626272</v>
       </c>
       <c r="U3">
         <v>5.3007432949812827</v>
       </c>
       <c r="V3">
-        <v>2.3128417767685341</v>
+        <v>2.3079576233724075</v>
       </c>
       <c r="W3">
-        <v>2.126858296867935</v>
+        <v>2.1201211138825826</v>
       </c>
       <c r="X3">
         <v>1.3050007295072739</v>
       </c>
       <c r="Y3">
-        <v>1.3053301509854149</v>
+        <v>1.3053292645434884</v>
       </c>
       <c r="Z3">
-        <v>1.3164708059591355</v>
+        <v>1.3164700096323136</v>
       </c>
       <c r="AA3">
         <v>761.04884161829943</v>
       </c>
       <c r="AB3">
-        <v>758.06559974569734</v>
+        <v>758.073456192446</v>
       </c>
       <c r="AC3">
-        <v>676.13564273360953</v>
+        <v>676.14045073717466</v>
       </c>
       <c r="AD3">
         <v>783.37546356326141</v>
       </c>
       <c r="AE3">
-        <v>698.51247219226138</v>
+        <v>698.4295752075891</v>
       </c>
       <c r="AF3">
-        <v>699.213771048154</v>
+        <v>699.31086212518687</v>
       </c>
       <c r="AG3">
         <v>816.08690480379</v>
       </c>
       <c r="AH3">
-        <v>729.00683772262346</v>
+        <v>728.81657990040571</v>
       </c>
       <c r="AI3">
-        <v>725.34780056244551</v>
+        <v>725.30905007485035</v>
       </c>
       <c r="AJ3">
         <v>510.48139409434015</v>
@@ -1237,118 +1237,118 @@
         <v>100</v>
       </c>
       <c r="AN3">
-        <v>926.13044943380169</v>
+        <v>927.15973501801523</v>
       </c>
       <c r="AO3">
-        <v>145.9097821527163</v>
+        <v>147.2800494353292</v>
       </c>
       <c r="AP3">
         <v>6.1230317691118863E-15</v>
       </c>
       <c r="AQ3">
-        <v>896.73361542274142</v>
+        <v>897.67971008746952</v>
       </c>
       <c r="AR3">
-        <v>2.7400691012432512</v>
+        <v>1.7634768590987235</v>
       </c>
       <c r="AS3">
         <v>100</v>
       </c>
       <c r="AT3">
-        <v>231.48743451711223</v>
+        <v>231.94032063432368</v>
       </c>
       <c r="AU3">
-        <v>145.8840517300419</v>
+        <v>147.26949144694035</v>
       </c>
       <c r="AV3">
         <v>520.183865298128</v>
       </c>
       <c r="AW3">
-        <v>450.307906682126</v>
+        <v>451.35224408865827</v>
       </c>
       <c r="AX3">
-        <v>503.60746181465851</v>
+        <v>504.94459084421788</v>
       </c>
       <c r="AY3">
         <v>510.48139409434015</v>
       </c>
       <c r="AZ3">
-        <v>-386.25222132840088</v>
+        <v>-387.19831599312886</v>
       </c>
       <c r="BA3">
-        <v>482.01485355352816</v>
+        <v>482.99144579567258</v>
       </c>
       <c r="BB3">
         <v>99.999999999999986</v>
       </c>
       <c r="BC3">
-        <v>231.48743451711223</v>
+        <v>231.94032063432368</v>
       </c>
       <c r="BD3">
-        <v>145.8840517300419</v>
+        <v>147.26949144694035</v>
       </c>
       <c r="BE3">
         <v>90</v>
       </c>
       <c r="BF3">
-        <v>14.474625580113761</v>
+        <v>14.487110650698016</v>
       </c>
       <c r="BG3">
-        <v>88.923967798535017</v>
+        <v>89.313945125986791</v>
       </c>
       <c r="BH3">
         <v>11.083520567472172</v>
       </c>
       <c r="BI3">
-        <v>149.0650360214932</v>
+        <v>149.07746245530029</v>
       </c>
       <c r="BJ3">
-        <v>16.838685210544362</v>
+        <v>16.9570498508353</v>
       </c>
       <c r="BK3">
-        <v>75.525374419886234</v>
+        <v>75.512889349301986</v>
       </c>
       <c r="BL3">
-        <v>132.22635081094884</v>
+        <v>132.120412604465</v>
       </c>
       <c r="BM3">
         <v>0.1313976114691395</v>
       </c>
       <c r="BN3">
-        <v>1.2217022507609945</v>
+        <v>1.2230473543749099</v>
       </c>
       <c r="BO3">
-        <v>0.21579957175871478</v>
+        <v>0.2178246387636687</v>
       </c>
       <c r="BP3">
         <v>0.66402879524975145</v>
       </c>
       <c r="BQ3">
-        <v>0.64466695242942118</v>
+        <v>0.64623873345355709</v>
       </c>
       <c r="BR3">
-        <v>0.72024820257719968</v>
+        <v>0.72206027132154771</v>
       </c>
       <c r="BS3">
         <v>0.12253596940639891</v>
       </c>
       <c r="BT3">
-        <v>1.2704002233051495</v>
+        <v>1.272144131442116</v>
       </c>
       <c r="BU3">
-        <v>0.20115837125248837</v>
+        <v>0.20305833688429811</v>
       </c>
       <c r="BV3">
         <v>0.63741234203873742</v>
       </c>
       <c r="BW3">
-        <v>0.61770052540091758</v>
+        <v>0.61929469846903928</v>
       </c>
       <c r="BX3">
-        <v>0.69429790980844464</v>
+        <v>0.69617853353974923</v>
       </c>
       <c r="BY3">
-        <v>0.10172736738377664</v>
+        <v>0.099795477565735258</v>
       </c>
     </row>
   </sheetData>
@@ -2140,106 +2140,106 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.886829876038094</v>
+        <v>0.88661849100439383</v>
       </c>
       <c r="C3">
         <v>1773</v>
       </c>
       <c r="D3">
-        <v>1758.9562299548395</v>
+        <v>1758.9932072717177</v>
       </c>
       <c r="E3">
-        <v>1394.1636317648961</v>
+        <v>1394.1838085136349</v>
       </c>
       <c r="F3">
         <v>1888.0124892904339</v>
       </c>
       <c r="G3">
-        <v>1501.1068902913933</v>
+        <v>1500.7475673723741</v>
       </c>
       <c r="H3">
-        <v>1507.5710589355535</v>
+        <v>1507.9909304382375</v>
       </c>
       <c r="I3">
         <v>1768.9494547516442</v>
       </c>
       <c r="J3">
-        <v>1436.7242028987939</v>
+        <v>1436.0393953717526</v>
       </c>
       <c r="K3">
-        <v>1381.6185921750066</v>
+        <v>1381.5625704990327</v>
       </c>
       <c r="L3">
         <v>2731.8</v>
       </c>
       <c r="M3">
-        <v>2414.4666913734436</v>
+        <v>2413.7074417616545</v>
       </c>
       <c r="N3">
-        <v>872.8720844382259</v>
+        <v>870.4517592730466</v>
       </c>
       <c r="O3">
         <v>2705.1966216148621</v>
       </c>
       <c r="P3">
-        <v>1016.5170773683535</v>
+        <v>1014.0352146956549</v>
       </c>
       <c r="Q3">
-        <v>840.660769468848</v>
+        <v>838.13784644841292</v>
       </c>
       <c r="R3">
         <v>5.34064271677014</v>
       </c>
       <c r="S3">
-        <v>4.7580047901266287</v>
+        <v>4.7564086043237728</v>
       </c>
       <c r="T3">
-        <v>2.1701879135223678</v>
+        <v>2.1641390095626272</v>
       </c>
       <c r="U3">
         <v>5.3007432949812827</v>
       </c>
       <c r="V3">
-        <v>2.4524488614793163</v>
+        <v>2.4476277699213393</v>
       </c>
       <c r="W3">
-        <v>2.1090802151273267</v>
+        <v>2.1028358569718293</v>
       </c>
       <c r="X3">
         <v>1.3050007295072739</v>
       </c>
       <c r="Y3">
-        <v>1.3053301509854149</v>
+        <v>1.3053292645434884</v>
       </c>
       <c r="Z3">
-        <v>1.3164708059591355</v>
+        <v>1.3164700096323136</v>
       </c>
       <c r="AA3">
         <v>761.04884161829943</v>
       </c>
       <c r="AB3">
-        <v>758.06559974569734</v>
+        <v>758.073456192446</v>
       </c>
       <c r="AC3">
-        <v>676.13564273360953</v>
+        <v>676.14045073717466</v>
       </c>
       <c r="AD3">
         <v>785.3451985431999</v>
       </c>
       <c r="AE3">
-        <v>700.30154127237847</v>
+        <v>700.21761684133253</v>
       </c>
       <c r="AF3">
-        <v>703.09798223863538</v>
+        <v>703.1957968578547</v>
       </c>
       <c r="AG3">
         <v>816.08690480379</v>
       </c>
       <c r="AH3">
-        <v>735.55905175981</v>
+        <v>735.3834808657615</v>
       </c>
       <c r="AI3">
-        <v>724.38501545358861</v>
+        <v>724.37011403590384</v>
       </c>
       <c r="AJ3">
         <v>532.86323571978437</v>
@@ -2254,118 +2254,118 @@
         <v>100</v>
       </c>
       <c r="AN3">
-        <v>891.54925936768836</v>
+        <v>892.54820797189382</v>
       </c>
       <c r="AO3">
-        <v>173.52400506279335</v>
+        <v>174.0503659306296</v>
       </c>
       <c r="AP3">
         <v>6.1230317691118863E-15</v>
       </c>
       <c r="AQ3">
-        <v>863.25008660391779</v>
+        <v>864.16869317101214</v>
       </c>
       <c r="AR3">
-        <v>-1.7310505108592154</v>
+        <v>-2.654004051447219</v>
       </c>
       <c r="AS3">
         <v>100</v>
       </c>
       <c r="AT3">
-        <v>222.84382391576858</v>
+        <v>223.28182482446738</v>
       </c>
       <c r="AU3">
-        <v>173.51537049253355</v>
+        <v>174.03012998639335</v>
       </c>
       <c r="AV3">
         <v>542.16531425549385</v>
       </c>
       <c r="AW3">
-        <v>398.51579779795</v>
+        <v>399.52231406257056</v>
       </c>
       <c r="AX3">
-        <v>549.82803935805771</v>
+        <v>550.86631236089511</v>
       </c>
       <c r="AY3">
         <v>532.86323571978426</v>
       </c>
       <c r="AZ3">
-        <v>-330.3868508841332</v>
+        <v>-331.30545745122754</v>
       </c>
       <c r="BA3">
-        <v>521.73105051085918</v>
+        <v>522.65400405144726</v>
       </c>
       <c r="BB3">
         <v>100</v>
       </c>
       <c r="BC3">
-        <v>222.84382391576855</v>
+        <v>223.28182482446738</v>
       </c>
       <c r="BD3">
-        <v>173.51537049253355</v>
+        <v>174.03012998639335</v>
       </c>
       <c r="BE3">
         <v>90</v>
       </c>
       <c r="BF3">
-        <v>14.474625580113765</v>
+        <v>14.487110650698016</v>
       </c>
       <c r="BG3">
-        <v>90.571583934412857</v>
+        <v>90.873707582421716</v>
       </c>
       <c r="BH3">
         <v>10.628810675006902</v>
       </c>
       <c r="BI3">
-        <v>146.00058653261351</v>
+        <v>146.02217683797608</v>
       </c>
       <c r="BJ3">
-        <v>18.395901452868202</v>
+        <v>18.416411019648969</v>
       </c>
       <c r="BK3">
-        <v>75.525374419886234</v>
+        <v>75.512889349301986</v>
       </c>
       <c r="BL3">
-        <v>127.60468507974528</v>
+        <v>127.60576581832713</v>
       </c>
       <c r="BM3">
         <v>0.1313976114691395</v>
       </c>
       <c r="BN3">
-        <v>1.1760845758820475</v>
+        <v>1.1773901337409574</v>
       </c>
       <c r="BO3">
-        <v>0.25664081893573537</v>
+        <v>0.2574174725692982</v>
       </c>
       <c r="BP3">
         <v>0.69035287318391958</v>
       </c>
       <c r="BQ3">
-        <v>0.56906314539003622</v>
+        <v>0.57056878383724141</v>
       </c>
       <c r="BR3">
-        <v>0.78200770482575932</v>
+        <v>0.78337543373037</v>
       </c>
       <c r="BS3">
         <v>0.12253596940639891</v>
       </c>
       <c r="BT3">
-        <v>1.2120702712238738</v>
+        <v>1.2137180548590831</v>
       </c>
       <c r="BU3">
-        <v>0.23954665179557547</v>
+        <v>0.24027822594845857</v>
       </c>
       <c r="BV3">
         <v>0.66434752360821847</v>
       </c>
       <c r="BW3">
-        <v>0.54178627377979927</v>
+        <v>0.543284319620854</v>
       </c>
       <c r="BX3">
-        <v>0.75902735096441987</v>
+        <v>0.7604763113316283</v>
       </c>
       <c r="BY3">
-        <v>0.17844872176257798</v>
+        <v>0.17669962459097488</v>
       </c>
     </row>
   </sheetData>
@@ -3157,106 +3157,106 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.886829876038094</v>
+        <v>0.88661849100439383</v>
       </c>
       <c r="C3">
         <v>1773</v>
       </c>
       <c r="D3">
-        <v>1758.9562299548395</v>
+        <v>1758.9932072717177</v>
       </c>
       <c r="E3">
-        <v>1394.1636317648961</v>
+        <v>1394.1838085136349</v>
       </c>
       <c r="F3">
         <v>1897.8771336944908</v>
       </c>
       <c r="G3">
-        <v>1509.2391393002395</v>
+        <v>1508.8746836164596</v>
       </c>
       <c r="H3">
-        <v>1525.1491430301244</v>
+        <v>1525.5742372019749</v>
       </c>
       <c r="I3">
         <v>1768.9494547516442</v>
       </c>
       <c r="J3">
-        <v>1459.4021428587535</v>
+        <v>1458.762910471421</v>
       </c>
       <c r="K3">
-        <v>1378.816023292469</v>
+        <v>1378.8554933623475</v>
       </c>
       <c r="L3">
         <v>2731.8</v>
       </c>
       <c r="M3">
-        <v>2414.4666913734436</v>
+        <v>2413.7074417616545</v>
       </c>
       <c r="N3">
-        <v>872.8720844382259</v>
+        <v>870.4517592730466</v>
       </c>
       <c r="O3">
         <v>2705.1966216148621</v>
       </c>
       <c r="P3">
-        <v>1086.906967686801</v>
+        <v>1084.4325919837384</v>
       </c>
       <c r="Q3">
-        <v>833.58987343100978</v>
+        <v>831.32734205310555</v>
       </c>
       <c r="R3">
         <v>5.34064271677014</v>
       </c>
       <c r="S3">
-        <v>4.7580047901266287</v>
+        <v>4.7564086043237728</v>
       </c>
       <c r="T3">
-        <v>2.1701879135223678</v>
+        <v>2.1641390095626272</v>
       </c>
       <c r="U3">
         <v>5.3007432949812827</v>
       </c>
       <c r="V3">
-        <v>2.581523496348725</v>
+        <v>2.5767752348378576</v>
       </c>
       <c r="W3">
-        <v>2.0955913344340948</v>
+        <v>2.0898436292929712</v>
       </c>
       <c r="X3">
         <v>1.3050007295072739</v>
       </c>
       <c r="Y3">
-        <v>1.3053301509854149</v>
+        <v>1.3053292645434884</v>
       </c>
       <c r="Z3">
-        <v>1.3164708059591355</v>
+        <v>1.3164700096323136</v>
       </c>
       <c r="AA3">
         <v>761.04884161829943</v>
       </c>
       <c r="AB3">
-        <v>758.06559974569734</v>
+        <v>758.073456192446</v>
       </c>
       <c r="AC3">
-        <v>676.13564273360953</v>
+        <v>676.14045073717466</v>
       </c>
       <c r="AD3">
         <v>787.39419398759424</v>
       </c>
       <c r="AE3">
-        <v>702.19592140297391</v>
+        <v>702.111028661933</v>
       </c>
       <c r="AF3">
-        <v>707.18511878717834</v>
+        <v>707.28357781321552</v>
       </c>
       <c r="AG3">
         <v>816.08690480379</v>
       </c>
       <c r="AH3">
-        <v>741.341530173079</v>
+        <v>741.17890331131161</v>
       </c>
       <c r="AI3">
-        <v>723.64994664438268</v>
+        <v>723.66008926639824</v>
       </c>
       <c r="AJ3">
         <v>555.24507734522865</v>
@@ -3271,118 +3271,118 @@
         <v>100</v>
       </c>
       <c r="AN3">
-        <v>859.60437389687445</v>
+        <v>860.57501414379067</v>
       </c>
       <c r="AO3">
-        <v>191.93045842804943</v>
+        <v>191.80996794204737</v>
       </c>
       <c r="AP3">
         <v>6.1230317691118863E-15</v>
       </c>
       <c r="AQ3">
-        <v>832.31918193490344</v>
+        <v>833.21212087592164</v>
       </c>
       <c r="AR3">
-        <v>-5.4877396598104644</v>
+        <v>-6.3634684949142386</v>
       </c>
       <c r="AS3">
         <v>100</v>
       </c>
       <c r="AT3">
-        <v>214.85916086090137</v>
+        <v>215.28334026123346</v>
       </c>
       <c r="AU3">
-        <v>191.85198874608352</v>
+        <v>191.70438198080782</v>
       </c>
       <c r="AV3">
         <v>564.17824835428473</v>
       </c>
       <c r="AW3">
-        <v>350.62019114708829</v>
+        <v>351.58582719334424</v>
       </c>
       <c r="AX3">
-        <v>592.64532196941707</v>
+        <v>593.42626233705175</v>
       </c>
       <c r="AY3">
         <v>555.24507734522876</v>
       </c>
       <c r="AZ3">
-        <v>-277.07410458967479</v>
+        <v>-277.96704353069288</v>
       </c>
       <c r="BA3">
-        <v>560.73281700503912</v>
+        <v>561.60854584014294</v>
       </c>
       <c r="BB3">
         <v>100</v>
       </c>
       <c r="BC3">
-        <v>214.85916086090137</v>
+        <v>215.28334026123346</v>
       </c>
       <c r="BD3">
-        <v>191.85198874608352</v>
+        <v>191.70438198080782</v>
       </c>
       <c r="BE3">
         <v>90</v>
       </c>
       <c r="BF3">
-        <v>14.474625580113768</v>
+        <v>14.487110650698016</v>
       </c>
       <c r="BG3">
-        <v>91.638443326607515</v>
+        <v>91.901187968024843</v>
       </c>
       <c r="BH3">
         <v>10.209559528764752</v>
       </c>
       <c r="BI3">
-        <v>142.2079467870515</v>
+        <v>142.24249303513696</v>
       </c>
       <c r="BJ3">
-        <v>18.888130957778408</v>
+        <v>18.847275417449438</v>
       </c>
       <c r="BK3">
-        <v>75.525374419886234</v>
+        <v>75.512889349301986</v>
       </c>
       <c r="BL3">
-        <v>123.31981582927308</v>
+        <v>123.39521761768751</v>
       </c>
       <c r="BM3">
         <v>0.1313976114691395</v>
       </c>
       <c r="BN3">
-        <v>1.1339445744342436</v>
+        <v>1.1352132265205226</v>
       </c>
       <c r="BO3">
-        <v>0.28386383781230129</v>
+        <v>0.28368361593057034</v>
       </c>
       <c r="BP3">
         <v>0.71651309174267752</v>
       </c>
       <c r="BQ3">
-        <v>0.49931960648041918</v>
+        <v>0.50075531196737988</v>
       </c>
       <c r="BR3">
-        <v>0.8380342094666855</v>
+        <v>0.83902168939339916</v>
       </c>
       <c r="BS3">
         <v>0.12253596940639891</v>
       </c>
       <c r="BT3">
-        <v>1.1595254533982264</v>
+        <v>1.1610894620705765</v>
       </c>
       <c r="BU3">
-        <v>0.26522555459037189</v>
+        <v>0.26505533576750434</v>
       </c>
       <c r="BV3">
         <v>0.69132128580096364</v>
       </c>
       <c r="BW3">
-        <v>0.47295366154008656</v>
+        <v>0.47436027337339143</v>
       </c>
       <c r="BX3">
-        <v>0.81896685644427447</v>
+        <v>0.82003453159705209</v>
       </c>
       <c r="BY3">
-        <v>0.24555213924589203</v>
+        <v>0.24395944815479909</v>
       </c>
     </row>
   </sheetData>
